--- a/Assets/Data/Commodore/C64/250469/Data C64 250469 v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C64/250469/Data C64 250469 v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Commodore\C64\250469\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C64\250469\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DA4E22-950D-4243-B770-05D16334767C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F2C2F-8EF6-4D5F-B100-1C71F74E567C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10136" uniqueCount="3044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10140" uniqueCount="3047">
   <si>
     <r>
       <t xml:space="preserve"># Hardware: </t>
@@ -9280,6 +9280,24 @@
     <t>Commodore/Shared files/Board local files/Commodore 64-128 Best-Practises.txt</t>
   </si>
   <si>
+    <t>Forum64; Repair Corner (primarily German)</t>
+  </si>
+  <si>
+    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
+  </si>
+  <si>
+    <t>f16a1341-e3bc-4c74-a5f2-2199843f887f</t>
+  </si>
+  <si>
+    <t>Zimmers; Character ROMs</t>
+  </si>
+  <si>
+    <t>https://www.zimmers.net/anonftp/pub/cbm/firmware/characters/</t>
+  </si>
+  <si>
+    <t>9f66b865-15b2-41ac-b9f5-0e26b9411d05</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -9291,17 +9309,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026-May-12</t>
+      <t>2026-June-24</t>
     </r>
-  </si>
-  <si>
-    <t>Forum64; Repair Corner (primarily German)</t>
-  </si>
-  <si>
-    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
-  </si>
-  <si>
-    <t>f16a1341-e3bc-4c74-a5f2-2199843f887f</t>
   </si>
 </sst>
 </file>
@@ -9997,7 +10006,7 @@
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>3040</v>
+        <v>3046</v>
       </c>
       <c r="I3"/>
     </row>
@@ -10101,8 +10110,12 @@
         <v>0.3</v>
       </c>
       <c r="E10" s="60"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="60"/>
+      <c r="F10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="60">
+        <v>1</v>
+      </c>
       <c r="H10" s="60"/>
       <c r="I10" t="s">
         <v>13</v>
@@ -12671,9 +12684,6 @@
       </c>
       <c r="C125" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>416</v>
@@ -50250,7 +50260,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -50335,51 +50345,51 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>283</v>
-      </c>
-      <c r="B11" t="s">
-        <v>857</v>
-      </c>
-      <c r="C11" t="s">
-        <v>858</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1955</v>
+    <row r="11" spans="1:4" s="64" customFormat="1">
+      <c r="A11" s="63" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>3043</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>3044</v>
+      </c>
+      <c r="D11" s="64" t="s">
+        <v>3045</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
-        <v>1995</v>
+        <v>857</v>
       </c>
       <c r="C12" t="s">
-        <v>1996</v>
+        <v>858</v>
       </c>
       <c r="D12" t="s">
-        <v>1997</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>859</v>
+        <v>1995</v>
       </c>
       <c r="C13" t="s">
-        <v>860</v>
+        <v>1996</v>
       </c>
       <c r="D13" t="s">
-        <v>1956</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B14" t="s">
         <v>859</v>
@@ -50388,31 +50398,42 @@
         <v>860</v>
       </c>
       <c r="D14" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>312</v>
+      </c>
+      <c r="B15" t="s">
+        <v>859</v>
+      </c>
+      <c r="C15" t="s">
+        <v>860</v>
+      </c>
+      <c r="D15" t="s">
         <v>1957</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="64" customFormat="1">
-      <c r="A15" s="64" t="s">
+    <row r="16" spans="1:4" s="64" customFormat="1">
+      <c r="A16" s="64" t="s">
         <v>400</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B16" s="64" t="s">
         <v>1991</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C16" s="64" t="s">
         <v>1992</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>1993</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="17"/>
-    </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="20"/>
-      <c r="D20" s="1"/>
+      <c r="A20" s="17"/>
     </row>
     <row r="21" spans="1:4">
+      <c r="A21" s="20"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4">
@@ -50422,28 +50443,28 @@
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="18"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="18"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="19"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="18"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="18"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="9"/>
-    </row>
-    <row r="37" spans="4:4">
-      <c r="D37" s="59"/>
-    </row>
-    <row r="39" spans="4:4">
-      <c r="D39" s="59"/>
-    </row>
-    <row r="52" spans="4:4">
-      <c r="D52" s="4"/>
-    </row>
-    <row r="58" spans="4:4">
-      <c r="D58" s="1"/>
+      <c r="A32" s="19"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="9"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="D38" s="59"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="D40" s="59"/>
+    </row>
+    <row r="53" spans="4:4">
+      <c r="D53" s="4"/>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="1"/>
@@ -50456,6 +50477,9 @@
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="4:4">
+      <c r="D63" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50934,13 +50958,13 @@
         <v>921</v>
       </c>
       <c r="B24" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C24" t="s">
         <v>3041</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>3042</v>
-      </c>
-      <c r="D24" t="s">
-        <v>3043</v>
       </c>
     </row>
     <row r="25" spans="1:4">
